--- a/templates/statement_template.xlsx
+++ b/templates/statement_template.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lovec\Documents\데일리시가\0.재무\거래업체관리\퍼프시가바\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DAILYCIGAR_DB\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1FFBFDC5-BF71-034F-A067-D38D8ECA8A9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7D96BCA-C92F-408D-98E8-D31A59E2521F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="49">
   <si>
     <t>거 래 명 세 서</t>
   </si>
@@ -203,6 +203,94 @@
   </si>
   <si>
     <t>010-9770-9311</t>
+    <phoneticPr fontId="15" type="noConversion"/>
+  </si>
+  <si>
+    <t>(주)데일리시가</t>
+    <phoneticPr fontId="15" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="0" tint="-0.499984740745262"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>경기도</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="0" tint="-0.499984740745262"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="0" tint="-0.499984740745262"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>수원시</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="0" tint="-0.499984740745262"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="0" tint="-0.499984740745262"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>영통구</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="0" tint="-0.499984740745262"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="0" tint="-0.499984740745262"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>덕영대로</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="0" tint="-0.499984740745262"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t>1470
+031-8043-8880</t>
+    </r>
     <phoneticPr fontId="15" type="noConversion"/>
   </si>
 </sst>
@@ -213,7 +301,7 @@
   <numFmts count="1">
     <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
   </numFmts>
-  <fonts count="19" x14ac:knownFonts="1">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -352,6 +440,34 @@
       <name val="Noto Sans CJK SC"/>
       <family val="3"/>
       <charset val="129"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="0" tint="-0.499984740745262"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="0" tint="-0.499984740745262"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="0" tint="-0.499984740745262"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="6">
@@ -668,7 +784,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -707,6 +823,39 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -716,14 +865,35 @@
     <xf numFmtId="0" fontId="8" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="14" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -734,36 +904,9 @@
     <xf numFmtId="3" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -782,35 +925,14 @@
     <xf numFmtId="0" fontId="9" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -998,168 +1120,6 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>830580</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>7620</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="1118896" cy="336246"/>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="7" name="TextBox 6">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DD5450E4-377C-3449-53FD-40309228B309}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="937260" y="541020"/>
-          <a:ext cx="1118896" cy="336246"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" rtlCol="0" anchor="t">
-          <a:spAutoFit/>
-        </a:bodyPr>
-        <a:lstStyle/>
-        <a:p>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="1"/>
-            <a:t>(</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" b="1"/>
-            <a:t>주</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="1"/>
-            <a:t>)</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" b="1"/>
-            <a:t>데일리시가</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>845820</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>15240</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="2061013" cy="491417"/>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="2" name="TextBox 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9DCBE362-7ABD-4D84-8D7C-2925B38D5B8E}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="952500" y="777240"/>
-          <a:ext cx="2061013" cy="491417"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" rtlCol="0" anchor="t">
-          <a:spAutoFit/>
-        </a:bodyPr>
-        <a:lstStyle/>
-        <a:p>
-          <a:r>
-            <a:rPr lang="ko-KR" altLang="en-US" sz="900" b="0">
-              <a:solidFill>
-                <a:schemeClr val="bg1">
-                  <a:lumMod val="50000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="맑은 고딕" panose="020B0503020000020004" pitchFamily="50" charset="-127"/>
-              <a:ea typeface="맑은 고딕" panose="020B0503020000020004" pitchFamily="50" charset="-127"/>
-            </a:rPr>
-            <a:t>경기도 수원시 영통구 덕영대로</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="900" b="0">
-              <a:solidFill>
-                <a:schemeClr val="bg1">
-                  <a:lumMod val="50000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="맑은 고딕" panose="020B0503020000020004" pitchFamily="50" charset="-127"/>
-              <a:ea typeface="맑은 고딕" panose="020B0503020000020004" pitchFamily="50" charset="-127"/>
-            </a:rPr>
-            <a:t>1470</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="900" b="0">
-              <a:solidFill>
-                <a:schemeClr val="bg1">
-                  <a:lumMod val="50000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="맑은 고딕" panose="020B0503020000020004" pitchFamily="50" charset="-127"/>
-              <a:ea typeface="맑은 고딕" panose="020B0503020000020004" pitchFamily="50" charset="-127"/>
-            </a:rPr>
-            <a:t>031-8043-8880</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -1346,60 +1306,70 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:J48"/>
-  <sheetFormatPr defaultColWidth="8.609375" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.5546875" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="1.61328125" customWidth="1"/>
-    <col min="2" max="2" width="16.94921875" customWidth="1"/>
-    <col min="3" max="3" width="13.98828125" customWidth="1"/>
-    <col min="4" max="4" width="7.93359375" customWidth="1"/>
-    <col min="5" max="5" width="10.0859375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="7.93359375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="4.70703125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.28125" customWidth="1"/>
-    <col min="9" max="9" width="9.01171875" customWidth="1"/>
-    <col min="10" max="10" width="11.1640625" customWidth="1"/>
-    <col min="11" max="11" width="1.61328125" customWidth="1"/>
+    <col min="1" max="1" width="1.6640625" customWidth="1"/>
+    <col min="2" max="2" width="17" customWidth="1"/>
+    <col min="3" max="3" width="14" customWidth="1"/>
+    <col min="4" max="4" width="7.88671875" customWidth="1"/>
+    <col min="5" max="5" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.88671875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="4.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.33203125" customWidth="1"/>
+    <col min="9" max="9" width="9" customWidth="1"/>
+    <col min="10" max="10" width="11.109375" customWidth="1"/>
+    <col min="11" max="11" width="1.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:10" ht="6" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="2" spans="2:10" ht="36" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B2" s="29" t="s">
+    <row r="1" spans="2:10" ht="6" customHeight="1"/>
+    <row r="2" spans="2:10" ht="36" customHeight="1">
+      <c r="B2" s="31" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="29"/>
-      <c r="D2" s="29"/>
-      <c r="I2" s="30" t="s">
+      <c r="C2" s="31"/>
+      <c r="D2" s="31"/>
+      <c r="I2" s="32" t="s">
         <v>43</v>
       </c>
-      <c r="J2" s="31"/>
-    </row>
-    <row r="3" spans="2:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B3" s="32"/>
-      <c r="C3" s="32"/>
-      <c r="D3" s="32"/>
-      <c r="H3" s="25" t="s">
+      <c r="J2" s="33"/>
+    </row>
+    <row r="3" spans="2:10" ht="18" customHeight="1">
+      <c r="B3" s="48"/>
+      <c r="C3" s="49" t="s">
+        <v>47</v>
+      </c>
+      <c r="D3" s="48"/>
+      <c r="H3" s="34" t="s">
         <v>44</v>
       </c>
-      <c r="I3" s="25"/>
-      <c r="J3" s="25"/>
-    </row>
-    <row r="4" spans="2:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I4" s="25" t="s">
+      <c r="I3" s="34"/>
+      <c r="J3" s="34"/>
+    </row>
+    <row r="4" spans="2:10" ht="13.5" customHeight="1">
+      <c r="C4" s="50" t="s">
+        <v>48</v>
+      </c>
+      <c r="D4" s="50"/>
+      <c r="E4" s="50"/>
+      <c r="I4" s="34" t="s">
         <v>45</v>
       </c>
-      <c r="J4" s="25"/>
-    </row>
-    <row r="5" spans="2:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I5" s="25" t="s">
+      <c r="J4" s="34"/>
+    </row>
+    <row r="5" spans="2:10" ht="13.5" customHeight="1">
+      <c r="C5" s="50"/>
+      <c r="D5" s="50"/>
+      <c r="E5" s="50"/>
+      <c r="I5" s="34" t="s">
         <v>46</v>
       </c>
-      <c r="J5" s="25"/>
-    </row>
-    <row r="6" spans="2:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I6" s="26"/>
-      <c r="J6" s="26"/>
-    </row>
-    <row r="7" spans="2:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J5" s="34"/>
+    </row>
+    <row r="6" spans="2:10" ht="13.5" customHeight="1">
+      <c r="I6" s="35"/>
+      <c r="J6" s="35"/>
+    </row>
+    <row r="7" spans="2:10" ht="13.5" customHeight="1">
       <c r="B7" s="1"/>
       <c r="C7" s="1"/>
       <c r="D7" s="1"/>
@@ -1410,85 +1380,85 @@
       <c r="I7" s="1"/>
       <c r="J7" s="1"/>
     </row>
-    <row r="8" spans="2:10" ht="9.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="9" spans="2:10" ht="4.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="10" spans="2:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B10" s="23" t="s">
+    <row r="8" spans="2:10" ht="9.75" customHeight="1"/>
+    <row r="9" spans="2:10" ht="4.5" customHeight="1"/>
+    <row r="10" spans="2:10" ht="18" customHeight="1">
+      <c r="B10" s="36" t="s">
         <v>1</v>
       </c>
-      <c r="C10" s="23"/>
-      <c r="D10" s="23"/>
-      <c r="E10" s="27" t="s">
+      <c r="C10" s="36"/>
+      <c r="D10" s="36"/>
+      <c r="E10" s="37" t="s">
         <v>2</v>
       </c>
-      <c r="F10" s="27"/>
-      <c r="G10" s="27"/>
-      <c r="H10" s="27"/>
-      <c r="I10" s="27"/>
-      <c r="J10" s="27"/>
-    </row>
-    <row r="11" spans="2:10" ht="4.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="12" spans="2:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="F10" s="37"/>
+      <c r="G10" s="37"/>
+      <c r="H10" s="37"/>
+      <c r="I10" s="37"/>
+      <c r="J10" s="37"/>
+    </row>
+    <row r="11" spans="2:10" ht="4.5" customHeight="1"/>
+    <row r="12" spans="2:10" ht="18" customHeight="1">
       <c r="B12" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C12" s="28">
+      <c r="C12" s="29">
         <v>20260314001</v>
       </c>
-      <c r="D12" s="28"/>
+      <c r="D12" s="29"/>
       <c r="E12" s="2"/>
       <c r="F12" s="2" t="s">
         <v>4</v>
       </c>
       <c r="G12" s="2"/>
-      <c r="H12" s="39" t="s">
+      <c r="H12" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="I12" s="39"/>
-      <c r="J12" s="39"/>
-    </row>
-    <row r="13" spans="2:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I12" s="17"/>
+      <c r="J12" s="17"/>
+    </row>
+    <row r="13" spans="2:10" ht="18" customHeight="1">
       <c r="B13" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C13" s="47">
+      <c r="C13" s="28">
         <v>46095</v>
       </c>
-      <c r="D13" s="28"/>
+      <c r="D13" s="29"/>
       <c r="E13" s="2"/>
       <c r="F13" s="2" t="s">
         <v>6</v>
       </c>
       <c r="G13" s="2"/>
-      <c r="H13" s="39" t="s">
+      <c r="H13" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="I13" s="39"/>
-      <c r="J13" s="39"/>
-    </row>
-    <row r="14" spans="2:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I13" s="17"/>
+      <c r="J13" s="17"/>
+    </row>
+    <row r="14" spans="2:10" ht="18" customHeight="1">
       <c r="B14" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C14" s="47">
+      <c r="C14" s="28">
         <v>46098</v>
       </c>
-      <c r="D14" s="28"/>
+      <c r="D14" s="29"/>
       <c r="E14" s="2"/>
       <c r="F14" s="2" t="s">
         <v>8</v>
       </c>
       <c r="G14" s="2"/>
-      <c r="H14" s="39" t="s">
+      <c r="H14" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="I14" s="40"/>
-      <c r="J14" s="40"/>
-    </row>
-    <row r="15" spans="2:10" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="I14" s="18"/>
+      <c r="J14" s="18"/>
+    </row>
+    <row r="15" spans="2:10" ht="18" customHeight="1" thickBot="1">
       <c r="B15" s="3"/>
-      <c r="C15" s="48"/>
-      <c r="D15" s="48"/>
+      <c r="C15" s="30"/>
+      <c r="D15" s="30"/>
       <c r="E15" s="1"/>
       <c r="F15" s="1"/>
       <c r="G15" s="1"/>
@@ -1496,14 +1466,14 @@
       <c r="I15" s="1"/>
       <c r="J15" s="1"/>
     </row>
-    <row r="16" spans="2:10" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25"/>
-    <row r="17" spans="2:10" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="41" t="s">
+    <row r="16" spans="2:10" ht="18" customHeight="1" thickBot="1"/>
+    <row r="17" spans="2:10" ht="18" customHeight="1" thickBot="1">
+      <c r="B17" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="C17" s="42"/>
-      <c r="D17" s="42"/>
-      <c r="E17" s="43"/>
+      <c r="C17" s="20"/>
+      <c r="D17" s="20"/>
+      <c r="E17" s="21"/>
       <c r="F17" s="4" t="s">
         <v>10</v>
       </c>
@@ -1520,13 +1490,13 @@
         <v>14</v>
       </c>
     </row>
-    <row r="18" spans="2:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B18" s="44" t="s">
+    <row r="18" spans="2:10" ht="18" customHeight="1">
+      <c r="B18" s="22" t="s">
         <v>26</v>
       </c>
-      <c r="C18" s="45"/>
-      <c r="D18" s="45"/>
-      <c r="E18" s="46"/>
+      <c r="C18" s="23"/>
+      <c r="D18" s="23"/>
+      <c r="E18" s="24"/>
       <c r="F18" s="6">
         <v>23000</v>
       </c>
@@ -1538,21 +1508,21 @@
         <v>46000</v>
       </c>
       <c r="I18" s="6">
-        <f>ROUND(H18*0.1,0)</f>
+        <f t="shared" ref="I18:I36" si="1">ROUND(H18*0.1,0)</f>
         <v>4600</v>
       </c>
       <c r="J18" s="7">
-        <f>H18+I18</f>
+        <f t="shared" ref="J18:J36" si="2">H18+I18</f>
         <v>50600</v>
       </c>
     </row>
-    <row r="19" spans="2:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B19" s="14" t="s">
+    <row r="19" spans="2:10" ht="18" customHeight="1">
+      <c r="B19" s="25" t="s">
         <v>27</v>
       </c>
-      <c r="C19" s="15"/>
-      <c r="D19" s="15"/>
-      <c r="E19" s="16"/>
+      <c r="C19" s="26"/>
+      <c r="D19" s="26"/>
+      <c r="E19" s="27"/>
       <c r="F19" s="8">
         <v>23000</v>
       </c>
@@ -1564,21 +1534,21 @@
         <v>46000</v>
       </c>
       <c r="I19" s="8">
-        <f>ROUND(H19*0.1,0)</f>
+        <f t="shared" si="1"/>
         <v>4600</v>
       </c>
       <c r="J19" s="9">
-        <f>H19+I19</f>
+        <f t="shared" si="2"/>
         <v>50600</v>
       </c>
     </row>
-    <row r="20" spans="2:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B20" s="17" t="s">
+    <row r="20" spans="2:10" ht="18" customHeight="1">
+      <c r="B20" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="C20" s="18"/>
-      <c r="D20" s="18"/>
-      <c r="E20" s="19"/>
+      <c r="C20" s="15"/>
+      <c r="D20" s="15"/>
+      <c r="E20" s="16"/>
       <c r="F20" s="6">
         <v>23000</v>
       </c>
@@ -1586,25 +1556,25 @@
         <v>2</v>
       </c>
       <c r="H20" s="6">
-        <f t="shared" ref="H20:H21" si="1">IF(AND(F20=0,G20=0),0,F20*G20)</f>
+        <f t="shared" ref="H20:H21" si="3">IF(AND(F20=0,G20=0),0,F20*G20)</f>
         <v>46000</v>
       </c>
       <c r="I20" s="6">
-        <f>ROUND(H20*0.1,0)</f>
+        <f t="shared" si="1"/>
         <v>4600</v>
       </c>
       <c r="J20" s="7">
-        <f>H20+I20</f>
+        <f t="shared" si="2"/>
         <v>50600</v>
       </c>
     </row>
-    <row r="21" spans="2:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B21" s="14" t="s">
+    <row r="21" spans="2:10" ht="18" customHeight="1">
+      <c r="B21" s="25" t="s">
         <v>29</v>
       </c>
-      <c r="C21" s="15"/>
-      <c r="D21" s="15"/>
-      <c r="E21" s="16"/>
+      <c r="C21" s="26"/>
+      <c r="D21" s="26"/>
+      <c r="E21" s="27"/>
       <c r="F21" s="8">
         <v>23000</v>
       </c>
@@ -1612,25 +1582,25 @@
         <v>2</v>
       </c>
       <c r="H21" s="8">
+        <f t="shared" si="3"/>
+        <v>46000</v>
+      </c>
+      <c r="I21" s="8">
         <f t="shared" si="1"/>
-        <v>46000</v>
-      </c>
-      <c r="I21" s="8">
-        <f>ROUND(H21*0.1,0)</f>
         <v>4600</v>
       </c>
       <c r="J21" s="9">
-        <f>H21+I21</f>
+        <f t="shared" si="2"/>
         <v>50600</v>
       </c>
     </row>
-    <row r="22" spans="2:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B22" s="17" t="s">
+    <row r="22" spans="2:10" ht="18" customHeight="1">
+      <c r="B22" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="C22" s="18"/>
-      <c r="D22" s="18"/>
-      <c r="E22" s="19"/>
+      <c r="C22" s="15"/>
+      <c r="D22" s="15"/>
+      <c r="E22" s="16"/>
       <c r="F22" s="6">
         <v>23000</v>
       </c>
@@ -1638,25 +1608,25 @@
         <v>2</v>
       </c>
       <c r="H22" s="6">
-        <f t="shared" ref="H22:H37" si="2">IF(AND(F22=0,G22=0),0,F22*G22)</f>
+        <f t="shared" ref="H22:H36" si="4">IF(AND(F22=0,G22=0),0,F22*G22)</f>
         <v>46000</v>
       </c>
       <c r="I22" s="6">
-        <f>ROUND(H22*0.1,0)</f>
+        <f t="shared" si="1"/>
         <v>4600</v>
       </c>
       <c r="J22" s="7">
-        <f>H22+I22</f>
+        <f t="shared" si="2"/>
         <v>50600</v>
       </c>
     </row>
-    <row r="23" spans="2:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B23" s="14" t="s">
+    <row r="23" spans="2:10" ht="18" customHeight="1">
+      <c r="B23" s="25" t="s">
         <v>31</v>
       </c>
-      <c r="C23" s="15"/>
-      <c r="D23" s="15"/>
-      <c r="E23" s="16"/>
+      <c r="C23" s="26"/>
+      <c r="D23" s="26"/>
+      <c r="E23" s="27"/>
       <c r="F23" s="8">
         <v>9000</v>
       </c>
@@ -1664,25 +1634,25 @@
         <v>5</v>
       </c>
       <c r="H23" s="8">
+        <f t="shared" si="4"/>
+        <v>45000</v>
+      </c>
+      <c r="I23" s="8">
+        <f t="shared" si="1"/>
+        <v>4500</v>
+      </c>
+      <c r="J23" s="9">
         <f t="shared" si="2"/>
-        <v>45000</v>
-      </c>
-      <c r="I23" s="8">
-        <f>ROUND(H23*0.1,0)</f>
-        <v>4500</v>
-      </c>
-      <c r="J23" s="9">
-        <f>H23+I23</f>
         <v>49500</v>
       </c>
     </row>
-    <row r="24" spans="2:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B24" s="17" t="s">
+    <row r="24" spans="2:10" ht="18" customHeight="1">
+      <c r="B24" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="C24" s="18"/>
-      <c r="D24" s="18"/>
-      <c r="E24" s="19"/>
+      <c r="C24" s="15"/>
+      <c r="D24" s="15"/>
+      <c r="E24" s="16"/>
       <c r="F24" s="6">
         <v>13000</v>
       </c>
@@ -1690,25 +1660,25 @@
         <v>5</v>
       </c>
       <c r="H24" s="6">
+        <f t="shared" si="4"/>
+        <v>65000</v>
+      </c>
+      <c r="I24" s="6">
+        <f t="shared" si="1"/>
+        <v>6500</v>
+      </c>
+      <c r="J24" s="7">
         <f t="shared" si="2"/>
-        <v>65000</v>
-      </c>
-      <c r="I24" s="6">
-        <f>ROUND(H24*0.1,0)</f>
-        <v>6500</v>
-      </c>
-      <c r="J24" s="7">
-        <f>H24+I24</f>
         <v>71500</v>
       </c>
     </row>
-    <row r="25" spans="2:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B25" s="14" t="s">
+    <row r="25" spans="2:10" ht="18" customHeight="1">
+      <c r="B25" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="C25" s="15"/>
-      <c r="D25" s="15"/>
-      <c r="E25" s="16"/>
+      <c r="C25" s="26"/>
+      <c r="D25" s="26"/>
+      <c r="E25" s="27"/>
       <c r="F25" s="8">
         <v>14000</v>
       </c>
@@ -1716,25 +1686,25 @@
         <v>5</v>
       </c>
       <c r="H25" s="8">
+        <f t="shared" si="4"/>
+        <v>70000</v>
+      </c>
+      <c r="I25" s="8">
+        <f t="shared" si="1"/>
+        <v>7000</v>
+      </c>
+      <c r="J25" s="9">
         <f t="shared" si="2"/>
-        <v>70000</v>
-      </c>
-      <c r="I25" s="8">
-        <f>ROUND(H25*0.1,0)</f>
-        <v>7000</v>
-      </c>
-      <c r="J25" s="9">
-        <f>H25+I25</f>
         <v>77000</v>
       </c>
     </row>
-    <row r="26" spans="2:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B26" s="17" t="s">
+    <row r="26" spans="2:10" ht="18" customHeight="1">
+      <c r="B26" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="C26" s="18"/>
-      <c r="D26" s="18"/>
-      <c r="E26" s="19"/>
+      <c r="C26" s="15"/>
+      <c r="D26" s="15"/>
+      <c r="E26" s="16"/>
       <c r="F26" s="6">
         <v>15000</v>
       </c>
@@ -1742,25 +1712,25 @@
         <v>5</v>
       </c>
       <c r="H26" s="6">
+        <f t="shared" si="4"/>
+        <v>75000</v>
+      </c>
+      <c r="I26" s="6">
+        <f t="shared" si="1"/>
+        <v>7500</v>
+      </c>
+      <c r="J26" s="7">
         <f t="shared" si="2"/>
-        <v>75000</v>
-      </c>
-      <c r="I26" s="6">
-        <f>ROUND(H26*0.1,0)</f>
-        <v>7500</v>
-      </c>
-      <c r="J26" s="7">
-        <f>H26+I26</f>
         <v>82500</v>
       </c>
     </row>
-    <row r="27" spans="2:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B27" s="14" t="s">
+    <row r="27" spans="2:10" ht="18" customHeight="1">
+      <c r="B27" s="25" t="s">
         <v>21</v>
       </c>
-      <c r="C27" s="15"/>
-      <c r="D27" s="15"/>
-      <c r="E27" s="16"/>
+      <c r="C27" s="26"/>
+      <c r="D27" s="26"/>
+      <c r="E27" s="27"/>
       <c r="F27" s="8">
         <v>16000</v>
       </c>
@@ -1768,25 +1738,25 @@
         <v>5</v>
       </c>
       <c r="H27" s="8">
+        <f t="shared" si="4"/>
+        <v>80000</v>
+      </c>
+      <c r="I27" s="8">
+        <f t="shared" si="1"/>
+        <v>8000</v>
+      </c>
+      <c r="J27" s="9">
         <f t="shared" si="2"/>
-        <v>80000</v>
-      </c>
-      <c r="I27" s="8">
-        <f>ROUND(H27*0.1,0)</f>
-        <v>8000</v>
-      </c>
-      <c r="J27" s="9">
-        <f>H27+I27</f>
         <v>88000</v>
       </c>
     </row>
-    <row r="28" spans="2:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B28" s="17" t="s">
+    <row r="28" spans="2:10" ht="18" customHeight="1">
+      <c r="B28" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="C28" s="18"/>
-      <c r="D28" s="18"/>
-      <c r="E28" s="19"/>
+      <c r="C28" s="15"/>
+      <c r="D28" s="15"/>
+      <c r="E28" s="16"/>
       <c r="F28" s="6">
         <v>21000</v>
       </c>
@@ -1794,25 +1764,25 @@
         <v>5</v>
       </c>
       <c r="H28" s="6">
+        <f t="shared" si="4"/>
+        <v>105000</v>
+      </c>
+      <c r="I28" s="6">
+        <f t="shared" si="1"/>
+        <v>10500</v>
+      </c>
+      <c r="J28" s="7">
         <f t="shared" si="2"/>
-        <v>105000</v>
-      </c>
-      <c r="I28" s="6">
-        <f>ROUND(H28*0.1,0)</f>
-        <v>10500</v>
-      </c>
-      <c r="J28" s="7">
-        <f>H28+I28</f>
         <v>115500</v>
       </c>
     </row>
-    <row r="29" spans="2:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B29" s="14" t="s">
+    <row r="29" spans="2:10" ht="18" customHeight="1">
+      <c r="B29" s="25" t="s">
         <v>35</v>
       </c>
-      <c r="C29" s="15"/>
-      <c r="D29" s="15"/>
-      <c r="E29" s="16"/>
+      <c r="C29" s="26"/>
+      <c r="D29" s="26"/>
+      <c r="E29" s="27"/>
       <c r="F29" s="8">
         <v>29000</v>
       </c>
@@ -1820,25 +1790,25 @@
         <v>5</v>
       </c>
       <c r="H29" s="8">
+        <f t="shared" si="4"/>
+        <v>145000</v>
+      </c>
+      <c r="I29" s="8">
+        <f t="shared" si="1"/>
+        <v>14500</v>
+      </c>
+      <c r="J29" s="9">
         <f t="shared" si="2"/>
-        <v>145000</v>
-      </c>
-      <c r="I29" s="8">
-        <f>ROUND(H29*0.1,0)</f>
-        <v>14500</v>
-      </c>
-      <c r="J29" s="9">
-        <f>H29+I29</f>
         <v>159500</v>
       </c>
     </row>
-    <row r="30" spans="2:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B30" s="17" t="s">
+    <row r="30" spans="2:10" ht="18" customHeight="1">
+      <c r="B30" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="C30" s="18"/>
-      <c r="D30" s="18"/>
-      <c r="E30" s="19"/>
+      <c r="C30" s="15"/>
+      <c r="D30" s="15"/>
+      <c r="E30" s="16"/>
       <c r="F30" s="6">
         <v>19000</v>
       </c>
@@ -1846,25 +1816,25 @@
         <v>5</v>
       </c>
       <c r="H30" s="6">
+        <f t="shared" si="4"/>
+        <v>95000</v>
+      </c>
+      <c r="I30" s="6">
+        <f t="shared" si="1"/>
+        <v>9500</v>
+      </c>
+      <c r="J30" s="7">
         <f t="shared" si="2"/>
-        <v>95000</v>
-      </c>
-      <c r="I30" s="6">
-        <f>ROUND(H30*0.1,0)</f>
-        <v>9500</v>
-      </c>
-      <c r="J30" s="7">
-        <f>H30+I30</f>
         <v>104500</v>
       </c>
     </row>
-    <row r="31" spans="2:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B31" s="14" t="s">
+    <row r="31" spans="2:10" ht="18" customHeight="1">
+      <c r="B31" s="25" t="s">
         <v>37</v>
       </c>
-      <c r="C31" s="15"/>
-      <c r="D31" s="15"/>
-      <c r="E31" s="16"/>
+      <c r="C31" s="26"/>
+      <c r="D31" s="26"/>
+      <c r="E31" s="27"/>
       <c r="F31" s="8">
         <v>26000</v>
       </c>
@@ -1872,25 +1842,25 @@
         <v>5</v>
       </c>
       <c r="H31" s="8">
+        <f t="shared" si="4"/>
+        <v>130000</v>
+      </c>
+      <c r="I31" s="8">
+        <f t="shared" si="1"/>
+        <v>13000</v>
+      </c>
+      <c r="J31" s="9">
         <f t="shared" si="2"/>
-        <v>130000</v>
-      </c>
-      <c r="I31" s="8">
-        <f>ROUND(H31*0.1,0)</f>
-        <v>13000</v>
-      </c>
-      <c r="J31" s="9">
-        <f>H31+I31</f>
         <v>143000</v>
       </c>
     </row>
-    <row r="32" spans="2:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B32" s="17" t="s">
+    <row r="32" spans="2:10" ht="18" customHeight="1">
+      <c r="B32" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="C32" s="18"/>
-      <c r="D32" s="18"/>
-      <c r="E32" s="19"/>
+      <c r="C32" s="15"/>
+      <c r="D32" s="15"/>
+      <c r="E32" s="16"/>
       <c r="F32" s="6">
         <v>30000</v>
       </c>
@@ -1898,25 +1868,25 @@
         <v>5</v>
       </c>
       <c r="H32" s="6">
+        <f t="shared" si="4"/>
+        <v>150000</v>
+      </c>
+      <c r="I32" s="6">
+        <f t="shared" si="1"/>
+        <v>15000</v>
+      </c>
+      <c r="J32" s="7">
         <f t="shared" si="2"/>
-        <v>150000</v>
-      </c>
-      <c r="I32" s="6">
-        <f>ROUND(H32*0.1,0)</f>
-        <v>15000</v>
-      </c>
-      <c r="J32" s="7">
-        <f>H32+I32</f>
         <v>165000</v>
       </c>
     </row>
-    <row r="33" spans="2:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B33" s="14" t="s">
+    <row r="33" spans="2:10" ht="18" customHeight="1">
+      <c r="B33" s="25" t="s">
         <v>39</v>
       </c>
-      <c r="C33" s="15"/>
-      <c r="D33" s="15"/>
-      <c r="E33" s="16"/>
+      <c r="C33" s="26"/>
+      <c r="D33" s="26"/>
+      <c r="E33" s="27"/>
       <c r="F33" s="8">
         <v>16000</v>
       </c>
@@ -1924,25 +1894,25 @@
         <v>5</v>
       </c>
       <c r="H33" s="8">
+        <f t="shared" si="4"/>
+        <v>80000</v>
+      </c>
+      <c r="I33" s="8">
+        <f t="shared" si="1"/>
+        <v>8000</v>
+      </c>
+      <c r="J33" s="9">
         <f t="shared" si="2"/>
-        <v>80000</v>
-      </c>
-      <c r="I33" s="8">
-        <f>ROUND(H33*0.1,0)</f>
-        <v>8000</v>
-      </c>
-      <c r="J33" s="9">
-        <f>H33+I33</f>
         <v>88000</v>
       </c>
     </row>
-    <row r="34" spans="2:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B34" s="17" t="s">
+    <row r="34" spans="2:10" ht="18" customHeight="1">
+      <c r="B34" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="C34" s="18"/>
-      <c r="D34" s="18"/>
-      <c r="E34" s="19"/>
+      <c r="C34" s="15"/>
+      <c r="D34" s="15"/>
+      <c r="E34" s="16"/>
       <c r="F34" s="6">
         <v>36000</v>
       </c>
@@ -1950,25 +1920,25 @@
         <v>5</v>
       </c>
       <c r="H34" s="6">
+        <f t="shared" si="4"/>
+        <v>180000</v>
+      </c>
+      <c r="I34" s="6">
+        <f t="shared" si="1"/>
+        <v>18000</v>
+      </c>
+      <c r="J34" s="7">
         <f t="shared" si="2"/>
-        <v>180000</v>
-      </c>
-      <c r="I34" s="6">
-        <f>ROUND(H34*0.1,0)</f>
-        <v>18000</v>
-      </c>
-      <c r="J34" s="7">
-        <f>H34+I34</f>
         <v>198000</v>
       </c>
     </row>
-    <row r="35" spans="2:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B35" s="14" t="s">
+    <row r="35" spans="2:10" ht="18" customHeight="1">
+      <c r="B35" s="25" t="s">
         <v>41</v>
       </c>
-      <c r="C35" s="15"/>
-      <c r="D35" s="15"/>
-      <c r="E35" s="16"/>
+      <c r="C35" s="26"/>
+      <c r="D35" s="26"/>
+      <c r="E35" s="27"/>
       <c r="F35" s="8">
         <v>39000</v>
       </c>
@@ -1976,25 +1946,25 @@
         <v>5</v>
       </c>
       <c r="H35" s="8">
+        <f t="shared" si="4"/>
+        <v>195000</v>
+      </c>
+      <c r="I35" s="8">
+        <f t="shared" si="1"/>
+        <v>19500</v>
+      </c>
+      <c r="J35" s="9">
         <f t="shared" si="2"/>
-        <v>195000</v>
-      </c>
-      <c r="I35" s="8">
-        <f>ROUND(H35*0.1,0)</f>
-        <v>19500</v>
-      </c>
-      <c r="J35" s="9">
-        <f>H35+I35</f>
         <v>214500</v>
       </c>
     </row>
-    <row r="36" spans="2:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B36" s="33" t="s">
+    <row r="36" spans="2:10" ht="18" customHeight="1">
+      <c r="B36" s="42" t="s">
         <v>42</v>
       </c>
-      <c r="C36" s="34"/>
-      <c r="D36" s="34"/>
-      <c r="E36" s="35"/>
+      <c r="C36" s="43"/>
+      <c r="D36" s="43"/>
+      <c r="E36" s="44"/>
       <c r="F36" s="6">
         <v>48000</v>
       </c>
@@ -2002,134 +1972,122 @@
         <v>5</v>
       </c>
       <c r="H36" s="8">
+        <f t="shared" si="4"/>
+        <v>240000</v>
+      </c>
+      <c r="I36" s="8">
+        <f t="shared" si="1"/>
+        <v>24000</v>
+      </c>
+      <c r="J36" s="9">
         <f t="shared" si="2"/>
-        <v>240000</v>
-      </c>
-      <c r="I36" s="8">
-        <f>ROUND(H36*0.1,0)</f>
-        <v>24000</v>
-      </c>
-      <c r="J36" s="9">
-        <f>H36+I36</f>
         <v>264000</v>
       </c>
     </row>
-    <row r="37" spans="2:10" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B37" s="36"/>
-      <c r="C37" s="37"/>
-      <c r="D37" s="37"/>
-      <c r="E37" s="38"/>
+    <row r="37" spans="2:10" ht="18" customHeight="1" thickBot="1">
+      <c r="B37" s="45"/>
+      <c r="C37" s="46"/>
+      <c r="D37" s="46"/>
+      <c r="E37" s="47"/>
       <c r="F37" s="10"/>
       <c r="G37" s="10"/>
       <c r="H37" s="10"/>
       <c r="I37" s="10"/>
       <c r="J37" s="11"/>
     </row>
-    <row r="38" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="39" spans="2:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:10" ht="15.75" customHeight="1"/>
+    <row r="39" spans="2:10" ht="18" customHeight="1">
       <c r="E39" s="12" t="s">
         <v>15</v>
       </c>
       <c r="F39" s="12"/>
       <c r="G39" s="12"/>
       <c r="H39" s="12"/>
-      <c r="I39" s="21">
+      <c r="I39" s="39">
         <f>SUM(H18:H37)</f>
         <v>1885000</v>
       </c>
-      <c r="J39" s="21"/>
-    </row>
-    <row r="40" spans="2:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J39" s="39"/>
+    </row>
+    <row r="40" spans="2:10" ht="18" customHeight="1">
       <c r="E40" s="12" t="s">
         <v>16</v>
       </c>
       <c r="F40" s="12"/>
       <c r="G40" s="12"/>
       <c r="H40" s="12"/>
-      <c r="I40" s="21">
+      <c r="I40" s="39">
         <f>SUM(I18:I37)</f>
         <v>188500</v>
       </c>
-      <c r="J40" s="21"/>
-    </row>
-    <row r="41" spans="2:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J40" s="39"/>
+    </row>
+    <row r="41" spans="2:10" ht="18" customHeight="1">
       <c r="E41" s="13" t="s">
         <v>17</v>
       </c>
       <c r="F41" s="13"/>
       <c r="G41" s="13"/>
       <c r="H41" s="13"/>
-      <c r="I41" s="22">
+      <c r="I41" s="40">
         <f>I39+I40</f>
         <v>2073500</v>
       </c>
-      <c r="J41" s="22"/>
-    </row>
-    <row r="42" spans="2:10" ht="6" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="43" spans="2:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B43" s="23" t="s">
+      <c r="J41" s="40"/>
+    </row>
+    <row r="42" spans="2:10" ht="6" customHeight="1"/>
+    <row r="43" spans="2:10" ht="13.5" customHeight="1">
+      <c r="B43" s="36" t="s">
         <v>18</v>
       </c>
-      <c r="C43" s="23"/>
-      <c r="D43" s="23"/>
-      <c r="E43" s="23"/>
-      <c r="F43" s="23"/>
-      <c r="G43" s="23"/>
-      <c r="H43" s="23"/>
-      <c r="I43" s="23"/>
-      <c r="J43" s="23"/>
-    </row>
-    <row r="44" spans="2:10" ht="45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B44" s="24" t="s">
+      <c r="C43" s="36"/>
+      <c r="D43" s="36"/>
+      <c r="E43" s="36"/>
+      <c r="F43" s="36"/>
+      <c r="G43" s="36"/>
+      <c r="H43" s="36"/>
+      <c r="I43" s="36"/>
+      <c r="J43" s="36"/>
+    </row>
+    <row r="44" spans="2:10" ht="45" customHeight="1">
+      <c r="B44" s="41" t="s">
         <v>19</v>
       </c>
-      <c r="C44" s="24"/>
-      <c r="D44" s="24"/>
-      <c r="E44" s="24"/>
-      <c r="F44" s="24"/>
-      <c r="G44" s="24"/>
-      <c r="H44" s="24"/>
-      <c r="I44" s="24"/>
-      <c r="J44" s="24"/>
-    </row>
-    <row r="45" spans="2:10" ht="7.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="46" spans="2:10" ht="9.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="47" spans="2:10" ht="49.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B47" s="20" t="s">
+      <c r="C44" s="41"/>
+      <c r="D44" s="41"/>
+      <c r="E44" s="41"/>
+      <c r="F44" s="41"/>
+      <c r="G44" s="41"/>
+      <c r="H44" s="41"/>
+      <c r="I44" s="41"/>
+      <c r="J44" s="41"/>
+    </row>
+    <row r="45" spans="2:10" ht="7.5" customHeight="1"/>
+    <row r="46" spans="2:10" ht="9.75" customHeight="1"/>
+    <row r="47" spans="2:10" ht="49.5" customHeight="1">
+      <c r="B47" s="38" t="s">
         <v>22</v>
       </c>
-      <c r="C47" s="20"/>
-      <c r="D47" s="20"/>
-      <c r="E47" s="20"/>
-      <c r="F47" s="20"/>
-      <c r="G47" s="20"/>
-      <c r="H47" s="20"/>
-      <c r="I47" s="20"/>
-      <c r="J47" s="20"/>
-    </row>
-    <row r="48" spans="2:10" ht="7.5" customHeight="1" x14ac:dyDescent="0.2"/>
+      <c r="C47" s="38"/>
+      <c r="D47" s="38"/>
+      <c r="E47" s="38"/>
+      <c r="F47" s="38"/>
+      <c r="G47" s="38"/>
+      <c r="H47" s="38"/>
+      <c r="I47" s="38"/>
+      <c r="J47" s="38"/>
+    </row>
+    <row r="48" spans="2:10" ht="7.5" customHeight="1"/>
   </sheetData>
   <mergeCells count="43">
-    <mergeCell ref="B20:E20"/>
-    <mergeCell ref="H13:J13"/>
-    <mergeCell ref="H14:J14"/>
-    <mergeCell ref="B17:E17"/>
-    <mergeCell ref="B18:E18"/>
-    <mergeCell ref="B19:E19"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="I2:J2"/>
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="I4:J4"/>
-    <mergeCell ref="H3:J3"/>
-    <mergeCell ref="I5:J5"/>
-    <mergeCell ref="I6:J6"/>
-    <mergeCell ref="B10:D10"/>
-    <mergeCell ref="E10:J10"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="H12:J12"/>
+    <mergeCell ref="B32:E32"/>
+    <mergeCell ref="B33:E33"/>
+    <mergeCell ref="C4:E5"/>
+    <mergeCell ref="B27:E27"/>
+    <mergeCell ref="B28:E28"/>
+    <mergeCell ref="B29:E29"/>
+    <mergeCell ref="B30:E30"/>
+    <mergeCell ref="B31:E31"/>
     <mergeCell ref="B21:E21"/>
     <mergeCell ref="B22:E22"/>
     <mergeCell ref="B23:E23"/>
@@ -2146,13 +2104,25 @@
     <mergeCell ref="B24:E24"/>
     <mergeCell ref="B25:E25"/>
     <mergeCell ref="B26:E26"/>
-    <mergeCell ref="B27:E27"/>
-    <mergeCell ref="B28:E28"/>
-    <mergeCell ref="B29:E29"/>
-    <mergeCell ref="B30:E30"/>
-    <mergeCell ref="B31:E31"/>
-    <mergeCell ref="B32:E32"/>
-    <mergeCell ref="B33:E33"/>
+    <mergeCell ref="I5:J5"/>
+    <mergeCell ref="I6:J6"/>
+    <mergeCell ref="B10:D10"/>
+    <mergeCell ref="E10:J10"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="H12:J12"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="I2:J2"/>
+    <mergeCell ref="I4:J4"/>
+    <mergeCell ref="H3:J3"/>
+    <mergeCell ref="B20:E20"/>
+    <mergeCell ref="H13:J13"/>
+    <mergeCell ref="H14:J14"/>
+    <mergeCell ref="B17:E17"/>
+    <mergeCell ref="B18:E18"/>
+    <mergeCell ref="B19:E19"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="C15:D15"/>
   </mergeCells>
   <phoneticPr fontId="15" type="noConversion"/>
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.5" header="0.511811023622047" footer="0.511811023622047"/>

--- a/templates/statement_template.xlsx
+++ b/templates/statement_template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DAILYCIGAR_DB\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7D96BCA-C92F-408D-98E8-D31A59E2521F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{257F4F1F-FD13-42AA-8ABB-E6D9A223AE39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3000" yWindow="3000" windowWidth="14892" windowHeight="8880" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="거래명세서" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="46">
   <si>
     <t>거 래 명 세 서</t>
   </si>
@@ -191,18 +191,6 @@
   </si>
   <si>
     <t>퍼프시가바</t>
-    <phoneticPr fontId="15" type="noConversion"/>
-  </si>
-  <si>
-    <t>분당구 운중동 1032-2, 1층</t>
-    <phoneticPr fontId="15" type="noConversion"/>
-  </si>
-  <si>
-    <t>퍼프시가바 대표님</t>
-    <phoneticPr fontId="15" type="noConversion"/>
-  </si>
-  <si>
-    <t>010-9770-9311</t>
     <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
@@ -784,7 +772,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -823,6 +811,33 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -832,6 +847,48 @@
     <xf numFmtId="0" fontId="8" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="8" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -856,15 +913,6 @@
     <xf numFmtId="0" fontId="8" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="14" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -874,65 +922,11 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="8" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1081,7 +1075,7 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>967740</xdr:colOff>
       <xdr:row>6</xdr:row>
-      <xdr:rowOff>121920</xdr:rowOff>
+      <xdr:rowOff>152400</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1323,51 +1317,45 @@
   <sheetData>
     <row r="1" spans="2:10" ht="6" customHeight="1"/>
     <row r="2" spans="2:10" ht="36" customHeight="1">
-      <c r="B2" s="31" t="s">
+      <c r="B2" s="37" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="31"/>
-      <c r="D2" s="31"/>
-      <c r="I2" s="32" t="s">
+      <c r="C2" s="37"/>
+      <c r="D2" s="37"/>
+      <c r="I2" s="38" t="s">
         <v>43</v>
       </c>
-      <c r="J2" s="33"/>
-    </row>
-    <row r="3" spans="2:10" ht="18" customHeight="1">
-      <c r="B3" s="48"/>
-      <c r="C3" s="49" t="s">
-        <v>47</v>
-      </c>
-      <c r="D3" s="48"/>
-      <c r="H3" s="34" t="s">
+      <c r="J2" s="39"/>
+    </row>
+    <row r="3" spans="2:10" ht="15.6">
+      <c r="B3" s="15"/>
+      <c r="C3" s="16" t="s">
         <v>44</v>
       </c>
-      <c r="I3" s="34"/>
-      <c r="J3" s="34"/>
+      <c r="D3" s="15"/>
+      <c r="H3" s="18"/>
+      <c r="I3" s="18"/>
+      <c r="J3" s="18"/>
     </row>
     <row r="4" spans="2:10" ht="13.5" customHeight="1">
-      <c r="C4" s="50" t="s">
-        <v>48</v>
-      </c>
-      <c r="D4" s="50"/>
-      <c r="E4" s="50"/>
-      <c r="I4" s="34" t="s">
+      <c r="C4" s="19" t="s">
         <v>45</v>
       </c>
-      <c r="J4" s="34"/>
+      <c r="D4" s="19"/>
+      <c r="E4" s="19"/>
+      <c r="I4" s="17"/>
+      <c r="J4" s="14"/>
     </row>
     <row r="5" spans="2:10" ht="13.5" customHeight="1">
-      <c r="C5" s="50"/>
-      <c r="D5" s="50"/>
-      <c r="E5" s="50"/>
-      <c r="I5" s="34" t="s">
-        <v>46</v>
-      </c>
-      <c r="J5" s="34"/>
+      <c r="C5" s="19"/>
+      <c r="D5" s="19"/>
+      <c r="E5" s="19"/>
+      <c r="I5" s="17"/>
+      <c r="J5" s="14"/>
     </row>
     <row r="6" spans="2:10" ht="13.5" customHeight="1">
-      <c r="I6" s="35"/>
-      <c r="J6" s="35"/>
+      <c r="I6" s="51"/>
+      <c r="J6" s="51"/>
     </row>
     <row r="7" spans="2:10" ht="13.5" customHeight="1">
       <c r="B7" s="1"/>
@@ -1383,82 +1371,82 @@
     <row r="8" spans="2:10" ht="9.75" customHeight="1"/>
     <row r="9" spans="2:10" ht="4.5" customHeight="1"/>
     <row r="10" spans="2:10" ht="18" customHeight="1">
-      <c r="B10" s="36" t="s">
+      <c r="B10" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="C10" s="36"/>
-      <c r="D10" s="36"/>
-      <c r="E10" s="37" t="s">
+      <c r="C10" s="29"/>
+      <c r="D10" s="29"/>
+      <c r="E10" s="52" t="s">
         <v>2</v>
       </c>
-      <c r="F10" s="37"/>
-      <c r="G10" s="37"/>
-      <c r="H10" s="37"/>
-      <c r="I10" s="37"/>
-      <c r="J10" s="37"/>
+      <c r="F10" s="52"/>
+      <c r="G10" s="52"/>
+      <c r="H10" s="52"/>
+      <c r="I10" s="52"/>
+      <c r="J10" s="52"/>
     </row>
     <row r="11" spans="2:10" ht="4.5" customHeight="1"/>
     <row r="12" spans="2:10" ht="18" customHeight="1">
       <c r="B12" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C12" s="29">
+      <c r="C12" s="49">
         <v>20260314001</v>
       </c>
-      <c r="D12" s="29"/>
+      <c r="D12" s="49"/>
       <c r="E12" s="2"/>
       <c r="F12" s="2" t="s">
         <v>4</v>
       </c>
       <c r="G12" s="2"/>
-      <c r="H12" s="17" t="s">
+      <c r="H12" s="40" t="s">
         <v>24</v>
       </c>
-      <c r="I12" s="17"/>
-      <c r="J12" s="17"/>
+      <c r="I12" s="40"/>
+      <c r="J12" s="40"/>
     </row>
     <row r="13" spans="2:10" ht="18" customHeight="1">
       <c r="B13" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C13" s="28">
+      <c r="C13" s="48">
         <v>46095</v>
       </c>
-      <c r="D13" s="29"/>
+      <c r="D13" s="49"/>
       <c r="E13" s="2"/>
       <c r="F13" s="2" t="s">
         <v>6</v>
       </c>
       <c r="G13" s="2"/>
-      <c r="H13" s="17" t="s">
+      <c r="H13" s="40" t="s">
         <v>23</v>
       </c>
-      <c r="I13" s="17"/>
-      <c r="J13" s="17"/>
+      <c r="I13" s="40"/>
+      <c r="J13" s="40"/>
     </row>
     <row r="14" spans="2:10" ht="18" customHeight="1">
       <c r="B14" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C14" s="28">
+      <c r="C14" s="48">
         <v>46098</v>
       </c>
-      <c r="D14" s="29"/>
+      <c r="D14" s="49"/>
       <c r="E14" s="2"/>
       <c r="F14" s="2" t="s">
         <v>8</v>
       </c>
       <c r="G14" s="2"/>
-      <c r="H14" s="17" t="s">
+      <c r="H14" s="40" t="s">
         <v>25</v>
       </c>
-      <c r="I14" s="18"/>
-      <c r="J14" s="18"/>
+      <c r="I14" s="41"/>
+      <c r="J14" s="41"/>
     </row>
     <row r="15" spans="2:10" ht="18" customHeight="1" thickBot="1">
       <c r="B15" s="3"/>
-      <c r="C15" s="30"/>
-      <c r="D15" s="30"/>
+      <c r="C15" s="50"/>
+      <c r="D15" s="50"/>
       <c r="E15" s="1"/>
       <c r="F15" s="1"/>
       <c r="G15" s="1"/>
@@ -1468,12 +1456,12 @@
     </row>
     <row r="16" spans="2:10" ht="18" customHeight="1" thickBot="1"/>
     <row r="17" spans="2:10" ht="18" customHeight="1" thickBot="1">
-      <c r="B17" s="19" t="s">
+      <c r="B17" s="42" t="s">
         <v>9</v>
       </c>
-      <c r="C17" s="20"/>
-      <c r="D17" s="20"/>
-      <c r="E17" s="21"/>
+      <c r="C17" s="43"/>
+      <c r="D17" s="43"/>
+      <c r="E17" s="44"/>
       <c r="F17" s="4" t="s">
         <v>10</v>
       </c>
@@ -1491,12 +1479,12 @@
       </c>
     </row>
     <row r="18" spans="2:10" ht="18" customHeight="1">
-      <c r="B18" s="22" t="s">
+      <c r="B18" s="45" t="s">
         <v>26</v>
       </c>
-      <c r="C18" s="23"/>
-      <c r="D18" s="23"/>
-      <c r="E18" s="24"/>
+      <c r="C18" s="46"/>
+      <c r="D18" s="46"/>
+      <c r="E18" s="47"/>
       <c r="F18" s="6">
         <v>23000</v>
       </c>
@@ -1517,12 +1505,12 @@
       </c>
     </row>
     <row r="19" spans="2:10" ht="18" customHeight="1">
-      <c r="B19" s="25" t="s">
+      <c r="B19" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="C19" s="26"/>
-      <c r="D19" s="26"/>
-      <c r="E19" s="27"/>
+      <c r="C19" s="21"/>
+      <c r="D19" s="21"/>
+      <c r="E19" s="22"/>
       <c r="F19" s="8">
         <v>23000</v>
       </c>
@@ -1543,12 +1531,12 @@
       </c>
     </row>
     <row r="20" spans="2:10" ht="18" customHeight="1">
-      <c r="B20" s="14" t="s">
+      <c r="B20" s="23" t="s">
         <v>28</v>
       </c>
-      <c r="C20" s="15"/>
-      <c r="D20" s="15"/>
-      <c r="E20" s="16"/>
+      <c r="C20" s="24"/>
+      <c r="D20" s="24"/>
+      <c r="E20" s="25"/>
       <c r="F20" s="6">
         <v>23000</v>
       </c>
@@ -1569,12 +1557,12 @@
       </c>
     </row>
     <row r="21" spans="2:10" ht="18" customHeight="1">
-      <c r="B21" s="25" t="s">
+      <c r="B21" s="20" t="s">
         <v>29</v>
       </c>
-      <c r="C21" s="26"/>
-      <c r="D21" s="26"/>
-      <c r="E21" s="27"/>
+      <c r="C21" s="21"/>
+      <c r="D21" s="21"/>
+      <c r="E21" s="22"/>
       <c r="F21" s="8">
         <v>23000</v>
       </c>
@@ -1595,12 +1583,12 @@
       </c>
     </row>
     <row r="22" spans="2:10" ht="18" customHeight="1">
-      <c r="B22" s="14" t="s">
+      <c r="B22" s="23" t="s">
         <v>30</v>
       </c>
-      <c r="C22" s="15"/>
-      <c r="D22" s="15"/>
-      <c r="E22" s="16"/>
+      <c r="C22" s="24"/>
+      <c r="D22" s="24"/>
+      <c r="E22" s="25"/>
       <c r="F22" s="6">
         <v>23000</v>
       </c>
@@ -1621,12 +1609,12 @@
       </c>
     </row>
     <row r="23" spans="2:10" ht="18" customHeight="1">
-      <c r="B23" s="25" t="s">
+      <c r="B23" s="20" t="s">
         <v>31</v>
       </c>
-      <c r="C23" s="26"/>
-      <c r="D23" s="26"/>
-      <c r="E23" s="27"/>
+      <c r="C23" s="21"/>
+      <c r="D23" s="21"/>
+      <c r="E23" s="22"/>
       <c r="F23" s="8">
         <v>9000</v>
       </c>
@@ -1647,12 +1635,12 @@
       </c>
     </row>
     <row r="24" spans="2:10" ht="18" customHeight="1">
-      <c r="B24" s="14" t="s">
+      <c r="B24" s="23" t="s">
         <v>32</v>
       </c>
-      <c r="C24" s="15"/>
-      <c r="D24" s="15"/>
-      <c r="E24" s="16"/>
+      <c r="C24" s="24"/>
+      <c r="D24" s="24"/>
+      <c r="E24" s="25"/>
       <c r="F24" s="6">
         <v>13000</v>
       </c>
@@ -1673,12 +1661,12 @@
       </c>
     </row>
     <row r="25" spans="2:10" ht="18" customHeight="1">
-      <c r="B25" s="25" t="s">
+      <c r="B25" s="20" t="s">
         <v>33</v>
       </c>
-      <c r="C25" s="26"/>
-      <c r="D25" s="26"/>
-      <c r="E25" s="27"/>
+      <c r="C25" s="21"/>
+      <c r="D25" s="21"/>
+      <c r="E25" s="22"/>
       <c r="F25" s="8">
         <v>14000</v>
       </c>
@@ -1699,12 +1687,12 @@
       </c>
     </row>
     <row r="26" spans="2:10" ht="18" customHeight="1">
-      <c r="B26" s="14" t="s">
+      <c r="B26" s="23" t="s">
         <v>34</v>
       </c>
-      <c r="C26" s="15"/>
-      <c r="D26" s="15"/>
-      <c r="E26" s="16"/>
+      <c r="C26" s="24"/>
+      <c r="D26" s="24"/>
+      <c r="E26" s="25"/>
       <c r="F26" s="6">
         <v>15000</v>
       </c>
@@ -1725,12 +1713,12 @@
       </c>
     </row>
     <row r="27" spans="2:10" ht="18" customHeight="1">
-      <c r="B27" s="25" t="s">
+      <c r="B27" s="20" t="s">
         <v>21</v>
       </c>
-      <c r="C27" s="26"/>
-      <c r="D27" s="26"/>
-      <c r="E27" s="27"/>
+      <c r="C27" s="21"/>
+      <c r="D27" s="21"/>
+      <c r="E27" s="22"/>
       <c r="F27" s="8">
         <v>16000</v>
       </c>
@@ -1751,12 +1739,12 @@
       </c>
     </row>
     <row r="28" spans="2:10" ht="18" customHeight="1">
-      <c r="B28" s="14" t="s">
+      <c r="B28" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="C28" s="15"/>
-      <c r="D28" s="15"/>
-      <c r="E28" s="16"/>
+      <c r="C28" s="24"/>
+      <c r="D28" s="24"/>
+      <c r="E28" s="25"/>
       <c r="F28" s="6">
         <v>21000</v>
       </c>
@@ -1777,12 +1765,12 @@
       </c>
     </row>
     <row r="29" spans="2:10" ht="18" customHeight="1">
-      <c r="B29" s="25" t="s">
+      <c r="B29" s="20" t="s">
         <v>35</v>
       </c>
-      <c r="C29" s="26"/>
-      <c r="D29" s="26"/>
-      <c r="E29" s="27"/>
+      <c r="C29" s="21"/>
+      <c r="D29" s="21"/>
+      <c r="E29" s="22"/>
       <c r="F29" s="8">
         <v>29000</v>
       </c>
@@ -1803,12 +1791,12 @@
       </c>
     </row>
     <row r="30" spans="2:10" ht="18" customHeight="1">
-      <c r="B30" s="14" t="s">
+      <c r="B30" s="23" t="s">
         <v>36</v>
       </c>
-      <c r="C30" s="15"/>
-      <c r="D30" s="15"/>
-      <c r="E30" s="16"/>
+      <c r="C30" s="24"/>
+      <c r="D30" s="24"/>
+      <c r="E30" s="25"/>
       <c r="F30" s="6">
         <v>19000</v>
       </c>
@@ -1829,12 +1817,12 @@
       </c>
     </row>
     <row r="31" spans="2:10" ht="18" customHeight="1">
-      <c r="B31" s="25" t="s">
+      <c r="B31" s="20" t="s">
         <v>37</v>
       </c>
-      <c r="C31" s="26"/>
-      <c r="D31" s="26"/>
-      <c r="E31" s="27"/>
+      <c r="C31" s="21"/>
+      <c r="D31" s="21"/>
+      <c r="E31" s="22"/>
       <c r="F31" s="8">
         <v>26000</v>
       </c>
@@ -1855,12 +1843,12 @@
       </c>
     </row>
     <row r="32" spans="2:10" ht="18" customHeight="1">
-      <c r="B32" s="14" t="s">
+      <c r="B32" s="23" t="s">
         <v>38</v>
       </c>
-      <c r="C32" s="15"/>
-      <c r="D32" s="15"/>
-      <c r="E32" s="16"/>
+      <c r="C32" s="24"/>
+      <c r="D32" s="24"/>
+      <c r="E32" s="25"/>
       <c r="F32" s="6">
         <v>30000</v>
       </c>
@@ -1881,12 +1869,12 @@
       </c>
     </row>
     <row r="33" spans="2:10" ht="18" customHeight="1">
-      <c r="B33" s="25" t="s">
+      <c r="B33" s="20" t="s">
         <v>39</v>
       </c>
-      <c r="C33" s="26"/>
-      <c r="D33" s="26"/>
-      <c r="E33" s="27"/>
+      <c r="C33" s="21"/>
+      <c r="D33" s="21"/>
+      <c r="E33" s="22"/>
       <c r="F33" s="8">
         <v>16000</v>
       </c>
@@ -1907,12 +1895,12 @@
       </c>
     </row>
     <row r="34" spans="2:10" ht="18" customHeight="1">
-      <c r="B34" s="14" t="s">
+      <c r="B34" s="23" t="s">
         <v>40</v>
       </c>
-      <c r="C34" s="15"/>
-      <c r="D34" s="15"/>
-      <c r="E34" s="16"/>
+      <c r="C34" s="24"/>
+      <c r="D34" s="24"/>
+      <c r="E34" s="25"/>
       <c r="F34" s="6">
         <v>36000</v>
       </c>
@@ -1933,12 +1921,12 @@
       </c>
     </row>
     <row r="35" spans="2:10" ht="18" customHeight="1">
-      <c r="B35" s="25" t="s">
+      <c r="B35" s="20" t="s">
         <v>41</v>
       </c>
-      <c r="C35" s="26"/>
-      <c r="D35" s="26"/>
-      <c r="E35" s="27"/>
+      <c r="C35" s="21"/>
+      <c r="D35" s="21"/>
+      <c r="E35" s="22"/>
       <c r="F35" s="8">
         <v>39000</v>
       </c>
@@ -1959,12 +1947,12 @@
       </c>
     </row>
     <row r="36" spans="2:10" ht="18" customHeight="1">
-      <c r="B36" s="42" t="s">
+      <c r="B36" s="31" t="s">
         <v>42</v>
       </c>
-      <c r="C36" s="43"/>
-      <c r="D36" s="43"/>
-      <c r="E36" s="44"/>
+      <c r="C36" s="32"/>
+      <c r="D36" s="32"/>
+      <c r="E36" s="33"/>
       <c r="F36" s="6">
         <v>48000</v>
       </c>
@@ -1985,10 +1973,10 @@
       </c>
     </row>
     <row r="37" spans="2:10" ht="18" customHeight="1" thickBot="1">
-      <c r="B37" s="45"/>
-      <c r="C37" s="46"/>
-      <c r="D37" s="46"/>
-      <c r="E37" s="47"/>
+      <c r="B37" s="34"/>
+      <c r="C37" s="35"/>
+      <c r="D37" s="35"/>
+      <c r="E37" s="36"/>
       <c r="F37" s="10"/>
       <c r="G37" s="10"/>
       <c r="H37" s="10"/>
@@ -2003,11 +1991,11 @@
       <c r="F39" s="12"/>
       <c r="G39" s="12"/>
       <c r="H39" s="12"/>
-      <c r="I39" s="39">
+      <c r="I39" s="27">
         <f>SUM(H18:H37)</f>
         <v>1885000</v>
       </c>
-      <c r="J39" s="39"/>
+      <c r="J39" s="27"/>
     </row>
     <row r="40" spans="2:10" ht="18" customHeight="1">
       <c r="E40" s="12" t="s">
@@ -2016,11 +2004,11 @@
       <c r="F40" s="12"/>
       <c r="G40" s="12"/>
       <c r="H40" s="12"/>
-      <c r="I40" s="39">
+      <c r="I40" s="27">
         <f>SUM(I18:I37)</f>
         <v>188500</v>
       </c>
-      <c r="J40" s="39"/>
+      <c r="J40" s="27"/>
     </row>
     <row r="41" spans="2:10" ht="18" customHeight="1">
       <c r="E41" s="13" t="s">
@@ -2029,65 +2017,74 @@
       <c r="F41" s="13"/>
       <c r="G41" s="13"/>
       <c r="H41" s="13"/>
-      <c r="I41" s="40">
+      <c r="I41" s="28">
         <f>I39+I40</f>
         <v>2073500</v>
       </c>
-      <c r="J41" s="40"/>
+      <c r="J41" s="28"/>
     </row>
     <row r="42" spans="2:10" ht="6" customHeight="1"/>
     <row r="43" spans="2:10" ht="13.5" customHeight="1">
-      <c r="B43" s="36" t="s">
+      <c r="B43" s="29" t="s">
         <v>18</v>
       </c>
-      <c r="C43" s="36"/>
-      <c r="D43" s="36"/>
-      <c r="E43" s="36"/>
-      <c r="F43" s="36"/>
-      <c r="G43" s="36"/>
-      <c r="H43" s="36"/>
-      <c r="I43" s="36"/>
-      <c r="J43" s="36"/>
+      <c r="C43" s="29"/>
+      <c r="D43" s="29"/>
+      <c r="E43" s="29"/>
+      <c r="F43" s="29"/>
+      <c r="G43" s="29"/>
+      <c r="H43" s="29"/>
+      <c r="I43" s="29"/>
+      <c r="J43" s="29"/>
     </row>
     <row r="44" spans="2:10" ht="45" customHeight="1">
-      <c r="B44" s="41" t="s">
+      <c r="B44" s="30" t="s">
         <v>19</v>
       </c>
-      <c r="C44" s="41"/>
-      <c r="D44" s="41"/>
-      <c r="E44" s="41"/>
-      <c r="F44" s="41"/>
-      <c r="G44" s="41"/>
-      <c r="H44" s="41"/>
-      <c r="I44" s="41"/>
-      <c r="J44" s="41"/>
+      <c r="C44" s="30"/>
+      <c r="D44" s="30"/>
+      <c r="E44" s="30"/>
+      <c r="F44" s="30"/>
+      <c r="G44" s="30"/>
+      <c r="H44" s="30"/>
+      <c r="I44" s="30"/>
+      <c r="J44" s="30"/>
     </row>
     <row r="45" spans="2:10" ht="7.5" customHeight="1"/>
     <row r="46" spans="2:10" ht="9.75" customHeight="1"/>
     <row r="47" spans="2:10" ht="49.5" customHeight="1">
-      <c r="B47" s="38" t="s">
+      <c r="B47" s="26" t="s">
         <v>22</v>
       </c>
-      <c r="C47" s="38"/>
-      <c r="D47" s="38"/>
-      <c r="E47" s="38"/>
-      <c r="F47" s="38"/>
-      <c r="G47" s="38"/>
-      <c r="H47" s="38"/>
-      <c r="I47" s="38"/>
-      <c r="J47" s="38"/>
+      <c r="C47" s="26"/>
+      <c r="D47" s="26"/>
+      <c r="E47" s="26"/>
+      <c r="F47" s="26"/>
+      <c r="G47" s="26"/>
+      <c r="H47" s="26"/>
+      <c r="I47" s="26"/>
+      <c r="J47" s="26"/>
     </row>
     <row r="48" spans="2:10" ht="7.5" customHeight="1"/>
   </sheetData>
-  <mergeCells count="43">
+  <mergeCells count="41">
     <mergeCell ref="B32:E32"/>
     <mergeCell ref="B33:E33"/>
-    <mergeCell ref="C4:E5"/>
-    <mergeCell ref="B27:E27"/>
-    <mergeCell ref="B28:E28"/>
-    <mergeCell ref="B29:E29"/>
+    <mergeCell ref="B31:E31"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="I2:J2"/>
+    <mergeCell ref="B20:E20"/>
+    <mergeCell ref="H13:J13"/>
+    <mergeCell ref="H14:J14"/>
+    <mergeCell ref="B17:E17"/>
+    <mergeCell ref="B18:E18"/>
+    <mergeCell ref="B19:E19"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="I6:J6"/>
+    <mergeCell ref="B10:D10"/>
     <mergeCell ref="B30:E30"/>
-    <mergeCell ref="B31:E31"/>
     <mergeCell ref="B21:E21"/>
     <mergeCell ref="B22:E22"/>
     <mergeCell ref="B23:E23"/>
@@ -2103,26 +2100,15 @@
     <mergeCell ref="B35:E35"/>
     <mergeCell ref="B24:E24"/>
     <mergeCell ref="B25:E25"/>
+    <mergeCell ref="H3:J3"/>
+    <mergeCell ref="C4:E5"/>
+    <mergeCell ref="B27:E27"/>
+    <mergeCell ref="B28:E28"/>
+    <mergeCell ref="B29:E29"/>
     <mergeCell ref="B26:E26"/>
-    <mergeCell ref="I5:J5"/>
-    <mergeCell ref="I6:J6"/>
-    <mergeCell ref="B10:D10"/>
     <mergeCell ref="E10:J10"/>
     <mergeCell ref="C12:D12"/>
     <mergeCell ref="H12:J12"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="I2:J2"/>
-    <mergeCell ref="I4:J4"/>
-    <mergeCell ref="H3:J3"/>
-    <mergeCell ref="B20:E20"/>
-    <mergeCell ref="H13:J13"/>
-    <mergeCell ref="H14:J14"/>
-    <mergeCell ref="B17:E17"/>
-    <mergeCell ref="B18:E18"/>
-    <mergeCell ref="B19:E19"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="C15:D15"/>
   </mergeCells>
   <phoneticPr fontId="15" type="noConversion"/>
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.5" header="0.511811023622047" footer="0.511811023622047"/>
